--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0013.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0013.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Ta nghe nói ngươi từ chức rồi chuyển về quê sống.</t>
+          <t>Tao nghe nói mày từ chức rồi chuyển về quê sống.</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Nhiều năm qua, ta sống ẩn dật, không còn bận tâm đến chuyện bên ngoài Hồng Trấn nữa.</t>
+          <t>Nhiều năm qua, ta sống ẩn dật, không còn bận tâm đến chuyện bên ngoài Hongzhen nữa.</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Và cậu, {Male=chàng trai;Female=cô gái} trẻ... Ta nên gọi cậu là gì nhỉ?</t>
+          <t>Và cậu, {Male=sir;Female=lady} trẻ... Ta nên gọi cậu là gì nhỉ?</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Dù là Cộng Hưởng Giả Được Chỉ Định của Sentinel, nhưng ta đã không còn cảm nhận được sự hiện diện của nó một thời gian rồi…</t>
+          <t>Dù là Resonator Được Chỉ Định của Sentinel, nhưng ta đã không còn cảm nhận được sự hiện diện của nó một thời gian rồi…</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Chuyện gì đang xảy ra vậy?</t>
+          <t>Có chuyện gì vậy?</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Ta chỉ... nỗi lo cho sự an toàn của nó cứ không ngừng dày vò ta.</t>
+          <t>Tao chỉ... nỗi lo cho sự an toàn của nó cứ không ngừng dày vò tao.</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Đi nghỉ ngơi đi. Ta lo được mà.</t>
+          <t>Đi nghỉ ngơi đi. Tao lo được mà.</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Tất nhiên là ta đáng tin rồi! Dù thỉnh thoảng ngủ quên không nghe thấy cậu gọi thôi...</t>
+          <t>Tất nhiên là tao đáng tin rồi! Dù thỉnh thoảng ngủ quên không nghe thấy cậu gọi thôi...</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Đừng lo, nếu có nguy hiểm nào đến gần, ta sẽ tỉnh dậy đúng lúc như lần trước thôi.</t>
+          <t>Đừng lo, nếu có nguy hiểm nào đến gần, tao sẽ tỉnh dậy đúng lúc như lần trước thôi.</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Hiếm lắm mới nghe cậu nói thế.</t>
+          <t>Hiếm lắm mới nghe mày nói thế.</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>...{Male=Anh;Female=Cô} chắc hẳn là vị khách quý mà Quý cô Xinyi từ Jinzhou đã nhắc đến.</t>
+          <t>...{Male=He;Female=She} chắc hẳn là vị khách quý mà Quý cô Xinyi từ Jinzhou đã nhắc đến.</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>À, ra vậy.</t>
+          <t>À, vậy à.</t>
         </is>
       </c>
     </row>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Đừng quên nhé: Ta là Người Dẫn Đường của cậu. Ta đã cùng cậu vượt núi để đảm bảo cậu gặp được Jinhsi đấy.</t>
+          <t>Đừng quên nhé: I am your Wayfinder. I journeyed with you into the mountains to ensure you meet up with Jinhsi.</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Trước khi cậu đi, có điều quan trọng ta cần nói với cậu.</t>
+          <t>Trước khi cậu đi, có điều quan trọng tao cần nói với cậu.</t>
         </is>
       </c>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Được rồi, ta sẽ kể cho ngươi nghe tất cả.</t>
+          <t>Được rồi, tao sẽ kể cho mày nghe tất cả.</t>
         </is>
       </c>
     </row>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Nhưng quyết định của ta không chỉ vì bổn phận Cộng Hưởng Giả được chỉ định.</t>
+          <t>Nhưng quyết định của ta không chỉ vì bổn phận Resonator được chỉ định.</t>
         </is>
       </c>
     </row>
@@ -22674,7 +22674,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Không, ta đang đợi một người.</t>
+          <t>Không, tao đang đợi một người.</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -24559,7 +24559,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -24754,7 +24754,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Sao cậu biết ta sẽ đến Tòa Thị Chính?</t>
+          <t>Sao cậu biết tao sẽ đến Tòa Thị Chính?</t>
         </is>
       </c>
     </row>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Cậu nghĩ người đó là ta à?</t>
+          <t>Cậu nghĩ người đó là tao à?</t>
         </is>
       </c>
     </row>
@@ -26184,7 +26184,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Đứa trẻ hồi sinh được gọi là Cộng Hưởng Giả Được Chọn của Sentinel, và sau này trở thành Quan Chấp Hành của Jinzhou...</t>
+          <t>Đứa trẻ hồi sinh được gọi là Resonator Được Chọn của Sentinel, và sau này trở thành Quan Chấp Hành của Jinzhou...</t>
         </is>
       </c>
     </row>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Và chào mừng, {Male=Ngài;Female=Nữ} Arbiter. Hay giờ ta nên gọi ngài là "Rover"?</t>
+          <t>Và chào mừng, {Male=Lord;Female=Lady} Arbiter. Hay giờ ta nên gọi ngài là "Rover"?</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Cậu là Cộng Hưởng Giả của ta, nhưng sức mạnh của cậu chỉ là một phần nhỏ so với ta.</t>
+          <t>Cậu là Resonator của ta, nhưng sức mạnh của cậu chỉ là một phần nhỏ so với ta.</t>
         </is>
       </c>
     </row>
@@ -30214,7 +30214,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Nếu có ai có thể đối đầu với cậu trong trận chiến... thì người đó chắc chắn phải là Cộng Hưởng Giả của cậu.</t>
+          <t>Nếu có ai có thể đối đầu với cậu trong trận chiến... thì người đó chắc chắn phải là Resonator của cậu.</t>
         </is>
       </c>
     </row>
@@ -30539,7 +30539,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Được rồi! Quan Đại Nhân của Kim Châu!</t>
+          <t>Được rồi! Quan Đại Nhân của Jinzhou!</t>
         </is>
       </c>
     </row>
@@ -30734,7 +30734,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>{Male=Ngài;Female=Nữ Ngài} Arbiter, tiểu nhân tò mò về lựa chọn của ngài lần này.</t>
+          <t>{Male=Lord;Female=Lady} Arbiter, tiểu nhân tò mò về lựa chọn của ngài lần này.</t>
         </is>
       </c>
     </row>
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Nhưng... nếu ta không làm gì, cậu sẽ dùng hết sức lực còn lại để đóng băng cả Jinzhou trong thời gian.</t>
+          <t>Nhưng... nếu tao không làm gì, cậu sẽ dùng hết sức lực còn lại để đóng băng cả Jinzhou trong thời gian.</t>
         </is>
       </c>
     </row>
@@ -32034,7 +32034,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Rời xa Kim Châu khiến ta đầy tiếc nuối, biết rằng có lẽ ta sẽ chẳng bao giờ được đắm mình trong ánh nắng rực rỡ hay chứng kiến vẻ tinh khôi của những bông tuyết nơi đây nữa.</t>
+          <t>Rời xa Jinzhou khiến ta đầy tiếc nuối, biết rằng có lẽ ta sẽ chẳng bao giờ được đắm mình trong ánh nắng rực rỡ hay chứng kiến vẻ tinh khôi của những bông tuyết nơi đây nữa.</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Cái gì đây?</t>
+          <t>Cái gì vậy?</t>
         </is>
       </c>
     </row>
